--- a/outputs/test1_rotulado.xlsx
+++ b/outputs/test1_rotulado.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c5</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>c234</t>
+          <t>c1</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c234</t>
         </is>
       </c>
     </row>
